--- a/data/trans_camb/P2C_R2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R2-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,02; 16,52</t>
+          <t>3,84; 16,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,06; -1,38</t>
+          <t>-13,57; -0,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-29,07; -18,13</t>
+          <t>-28,79; -17,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,1; 26,19</t>
+          <t>10,0; 25,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 14,02</t>
+          <t>-1,18; 14,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-29,7; -17,39</t>
+          <t>-29,32; -17,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,78; 18,01</t>
+          <t>8,43; 18,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 3,19</t>
+          <t>-6,22; 3,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-27,17; -19,18</t>
+          <t>-26,98; -18,86</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,15; 54,63</t>
+          <t>9,71; 54,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-38,15; -4,43</t>
+          <t>-37,55; -3,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-77,21; -58,05</t>
+          <t>-77,51; -58,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25,79; 81,34</t>
+          <t>24,2; 78,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 43,8</t>
+          <t>-3,03; 43,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-71,66; -53,04</t>
+          <t>-71,26; -52,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,34; 55,23</t>
+          <t>22,44; 57,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-16,34; 9,55</t>
+          <t>-16,91; 10,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-72,09; -58,78</t>
+          <t>-71,89; -58,64</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,74; 23,47</t>
+          <t>8,48; 22,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 15,59</t>
+          <t>1,63; 15,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-25,5; -14,66</t>
+          <t>-26,15; -14,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,29; 30,4</t>
+          <t>13,81; 29,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 15,57</t>
+          <t>0,79; 16,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-31,37; -19,78</t>
+          <t>-31,02; -19,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,72; 23,44</t>
+          <t>12,66; 23,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,1; 13,5</t>
+          <t>3,8; 13,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-26,99; -18,61</t>
+          <t>-26,99; -19,08</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,34; 91,28</t>
+          <t>25,9; 89,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,25; 61,7</t>
+          <t>4,59; 62,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-77,93; -57,06</t>
+          <t>-77,54; -55,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32,1; 84,37</t>
+          <t>30,57; 81,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,19; 42,46</t>
+          <t>2,22; 45,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-71,51; -53,84</t>
+          <t>-71,06; -53,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,88; 73,16</t>
+          <t>33,87; 74,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,32; 41,52</t>
+          <t>9,94; 44,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-72,25; -57,74</t>
+          <t>-72,18; -58,4</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,02; 20,41</t>
+          <t>8,44; 19,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 7,92</t>
+          <t>-3,19; 8,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-30,98; -13,5</t>
+          <t>-30,03; -13,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 13,42</t>
+          <t>-5,65; 14,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,63; 5,76</t>
+          <t>-16,2; 6,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-40,93; -24,23</t>
+          <t>-40,33; -22,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,7; 16,56</t>
+          <t>7,43; 17,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 5,53</t>
+          <t>-4,61; 5,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-32,27; -17,49</t>
+          <t>-31,93; -17,83</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>27,08; 72,37</t>
+          <t>23,91; 68,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 27,87</t>
+          <t>-9,3; 28,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-88,52; -43,75</t>
+          <t>-88,99; -42,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 32,73</t>
+          <t>-11,18; 37,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-31,04; 14,31</t>
+          <t>-32,33; 15,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-79,82; -60,71</t>
+          <t>-79,39; -57,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,33; 51,97</t>
+          <t>20,16; 54,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-13,43; 17,17</t>
+          <t>-12,64; 18,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-87,54; -52,32</t>
+          <t>-86,33; -52,69</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,1; 23,07</t>
+          <t>14,82; 23,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 6,16</t>
+          <t>-1,37; 6,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-17,6; -11,22</t>
+          <t>-17,51; -10,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,42; 23,66</t>
+          <t>13,77; 23,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 9,99</t>
+          <t>-0,25; 9,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-24,67; 27,67</t>
+          <t>-24,35; 24,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,04; 22,37</t>
+          <t>15,72; 22,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 7,33</t>
+          <t>1,3; 7,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-18,56; 13,23</t>
+          <t>-18,16; 15,96</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>48,77; 83,72</t>
+          <t>47,64; 83,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 22,17</t>
+          <t>-4,47; 22,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-57,24; -40,3</t>
+          <t>-57,1; -38,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32,32; 65,21</t>
+          <t>33,21; 65,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 28,16</t>
+          <t>-0,63; 27,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-62,17; 79,54</t>
+          <t>-61,99; 68,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,13; 71,8</t>
+          <t>45,83; 71,37</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,42; 23,74</t>
+          <t>3,77; 23,18</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-55,68; 42,49</t>
+          <t>-55,01; 51,14</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,52; 20,94</t>
+          <t>8,03; 20,87</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 9,73</t>
+          <t>-3,02; 9,58</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-22,59; -11,1</t>
+          <t>-22,15; -11,42</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12,7; 23,87</t>
+          <t>11,76; 22,96</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 8,48</t>
+          <t>-3,15; 8,05</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-25,8; -14,31</t>
+          <t>-26,45; -14,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,34; 20,73</t>
+          <t>12,38; 20,15</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 6,81</t>
+          <t>-1,59; 6,66</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-22,66; -14,29</t>
+          <t>-22,97; -14,66</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>23,4; 82,72</t>
+          <t>23,62; 80,22</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 37,05</t>
+          <t>-8,91; 38,49</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-67,93; -42,58</t>
+          <t>-67,22; -42,79</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>30,58; 69,35</t>
+          <t>28,0; 65,15</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 24,59</t>
+          <t>-7,72; 23,09</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-64,55; -42,24</t>
+          <t>-65,1; -42,63</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,63; 64,73</t>
+          <t>32,15; 62,94</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 21,09</t>
+          <t>-4,21; 20,98</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-62,41; -44,86</t>
+          <t>-62,48; -45,31</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>6,37; 20,35</t>
+          <t>6,09; 21,05</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 11,14</t>
+          <t>-2,64; 11,01</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-16,37; -4,2</t>
+          <t>-17,0; -4,01</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10,53; 18,4</t>
+          <t>10,54; 18,17</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 5,55</t>
+          <t>-2,04; 5,61</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,6; -1,35</t>
+          <t>-8,96; -1,57</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,87; 18,11</t>
+          <t>10,9; 17,82</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 5,43</t>
+          <t>-1,2; 5,16</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-10,0; -3,62</t>
+          <t>-9,97; -3,67</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>27,77; 139,67</t>
+          <t>29,28; 144,38</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-14,94; 75,8</t>
+          <t>-12,91; 77,93</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-81,5; -24,83</t>
+          <t>-81,09; -19,61</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>36,47; 73,0</t>
+          <t>36,36; 71,74</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 21,59</t>
+          <t>-7,25; 22,13</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-30,03; -5,25</t>
+          <t>-31,24; -6,39</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>40,61; 77,62</t>
+          <t>40,62; 76,16</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 22,44</t>
+          <t>-4,41; 21,44</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-37,85; -15,72</t>
+          <t>-37,22; -14,93</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>13,24; 18,07</t>
+          <t>13,14; 18,04</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 4,54</t>
+          <t>-0,16; 4,4</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-20,48; -15,44</t>
+          <t>-20,51; -15,42</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14,55; 19,4</t>
+          <t>14,85; 19,54</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,52; 6,44</t>
+          <t>1,78; 6,48</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-17,95; 1,53</t>
+          <t>-18,0; 2,1</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,63; 18,1</t>
+          <t>14,56; 18,1</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,92</t>
+          <t>1,67; 4,93</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-18,11; -6,54</t>
+          <t>-18,0; -6,41</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>43,03; 64,18</t>
+          <t>43,12; 64,83</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 16,11</t>
+          <t>-0,55; 15,31</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-68,42; -54,3</t>
+          <t>-68,56; -54,3</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>40,32; 58,32</t>
+          <t>41,3; 58,62</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>4,26; 19,22</t>
+          <t>4,85; 19,37</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-51,77; 4,42</t>
+          <t>-51,73; 6,15</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>44,61; 58,04</t>
+          <t>44,66; 58,37</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>5,04; 15,86</t>
+          <t>5,11; 15,92</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-56,15; -20,89</t>
+          <t>-56,16; -20,36</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R2-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-23,46</t>
+          <t>-22,95</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-23,04</t>
+          <t>-22,85</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-23,06</t>
+          <t>-22,7</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,84; 16,91</t>
+          <t>3,31; 16,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,57; -0,93</t>
+          <t>-14,19; -1,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-28,79; -17,76</t>
+          <t>-28,26; -17,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,0; 25,56</t>
+          <t>9,14; 25,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 14,31</t>
+          <t>-1,48; 14,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-29,32; -17,09</t>
+          <t>-29,36; -16,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,43; 18,7</t>
+          <t>8,11; 18,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 3,39</t>
+          <t>-6,32; 3,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-26,98; -18,86</t>
+          <t>-26,42; -18,82</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-69,03%</t>
+          <t>-67,54%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-62,91%</t>
+          <t>-62,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-65,84%</t>
+          <t>-64,82%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,71; 54,18</t>
+          <t>9,1; 53,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-37,55; -3,27</t>
+          <t>-37,69; -4,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-77,51; -58,15</t>
+          <t>-76,16; -55,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24,2; 78,36</t>
+          <t>22,75; 80,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 43,57</t>
+          <t>-3,54; 43,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-71,26; -52,26</t>
+          <t>-70,84; -51,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,44; 57,78</t>
+          <t>21,17; 56,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 10,18</t>
+          <t>-17,05; 10,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-71,89; -58,64</t>
+          <t>-70,52; -57,31</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-19,96</t>
+          <t>-19,33</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-25,54</t>
+          <t>-25,28</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-23,0</t>
+          <t>-22,5</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,48; 22,8</t>
+          <t>9,1; 24,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,63; 15,81</t>
+          <t>1,16; 16,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-26,15; -14,37</t>
+          <t>-24,82; -13,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,81; 29,59</t>
+          <t>14,25; 29,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 16,15</t>
+          <t>1,18; 15,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-31,02; -19,84</t>
+          <t>-31,27; -19,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,66; 23,85</t>
+          <t>12,88; 23,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,8; 13,97</t>
+          <t>3,5; 13,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-26,99; -19,08</t>
+          <t>-26,79; -18,39</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-67,88%</t>
+          <t>-65,72%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-63,53%</t>
+          <t>-62,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-66,03%</t>
+          <t>-64,58%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,9; 89,27</t>
+          <t>27,08; 93,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,59; 62,66</t>
+          <t>3,22; 61,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-77,54; -55,04</t>
+          <t>-75,75; -52,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30,57; 81,58</t>
+          <t>31,86; 82,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,22; 45,64</t>
+          <t>2,53; 43,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-71,06; -53,49</t>
+          <t>-70,91; -53,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,87; 74,53</t>
+          <t>34,28; 73,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,94; 44,41</t>
+          <t>9,34; 42,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-72,18; -58,4</t>
+          <t>-71,48; -57,22</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-20,75</t>
+          <t>-13,84</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-32,12</t>
+          <t>-32,46</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-23,54</t>
+          <t>-18,44</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,44; 19,52</t>
+          <t>8,24; 20,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 8,01</t>
+          <t>-3,37; 7,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-30,03; -13,02</t>
+          <t>-18,73; -8,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 14,8</t>
+          <t>-7,07; 13,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,2; 6,14</t>
+          <t>-15,55; 6,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-40,33; -22,64</t>
+          <t>-40,89; -23,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,43; 17,15</t>
+          <t>6,77; 17,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 5,95</t>
+          <t>-4,73; 5,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-31,93; -17,83</t>
+          <t>-23,03; -13,72</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-66,75%</t>
+          <t>-44,52%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-70,79%</t>
+          <t>-71,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-68,32%</t>
+          <t>-53,53%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23,91; 68,92</t>
+          <t>22,92; 70,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 28,76</t>
+          <t>-10,09; 28,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-88,99; -42,7</t>
+          <t>-55,93; -28,17</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-11,18; 37,63</t>
+          <t>-14,04; 34,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-32,33; 15,71</t>
+          <t>-30,84; 18,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-79,39; -57,67</t>
+          <t>-80,32; -59,31</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,16; 54,86</t>
+          <t>18,8; 54,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-12,64; 18,46</t>
+          <t>-12,84; 17,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-86,33; -52,69</t>
+          <t>-62,11; -43,11</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-14,28</t>
+          <t>-13,24</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-5,29</t>
+          <t>-22,75</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-8,81</t>
+          <t>-16,74</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14,82; 23,14</t>
+          <t>14,91; 23,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 6,15</t>
+          <t>-1,38; 6,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-17,51; -10,65</t>
+          <t>-16,55; -10,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,77; 23,46</t>
+          <t>13,52; 23,8</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 9,89</t>
+          <t>0,32; 9,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-24,35; 24,02</t>
+          <t>-27,0; -18,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,72; 22,07</t>
+          <t>16,0; 22,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 7,27</t>
+          <t>1,01; 6,92</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-18,16; 15,96</t>
+          <t>-19,27; -13,93</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-48,81%</t>
+          <t>-45,25%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-13,76%</t>
+          <t>-59,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-27,02%</t>
+          <t>-51,33%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>47,64; 83,56</t>
+          <t>47,51; 84,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 22,04</t>
+          <t>-4,39; 23,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-57,1; -38,61</t>
+          <t>-53,42; -36,13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33,21; 65,91</t>
+          <t>31,93; 66,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 27,22</t>
+          <t>0,69; 28,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-61,99; 68,77</t>
+          <t>-65,6; -52,42</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,83; 71,37</t>
+          <t>46,88; 71,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,77; 23,18</t>
+          <t>3,02; 22,57</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-55,01; 51,14</t>
+          <t>-56,67; -44,58</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-16,63</t>
+          <t>-17,32</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-19,81</t>
+          <t>-16,48</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-18,49</t>
+          <t>-17,03</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,03; 20,87</t>
+          <t>7,96; 20,84</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 9,58</t>
+          <t>-2,52; 9,75</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-22,15; -11,42</t>
+          <t>-23,12; -11,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11,76; 22,96</t>
+          <t>12,91; 23,56</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 8,05</t>
+          <t>-2,85; 8,15</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-26,45; -14,94</t>
+          <t>-21,17; -11,95</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,38; 20,15</t>
+          <t>12,2; 21,18</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 6,66</t>
+          <t>-1,39; 6,78</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-22,97; -14,66</t>
+          <t>-20,91; -13,42</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-56,61%</t>
+          <t>-58,95%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-52,22%</t>
+          <t>-43,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-53,32%</t>
+          <t>-49,11%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>23,62; 80,22</t>
+          <t>22,33; 80,51</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 38,49</t>
+          <t>-7,51; 37,94</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-67,22; -42,79</t>
+          <t>-68,83; -45,7</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>28,0; 65,15</t>
+          <t>31,34; 67,72</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 23,09</t>
+          <t>-6,85; 23,33</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-65,1; -42,63</t>
+          <t>-51,25; -33,58</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,15; 62,94</t>
+          <t>33,66; 66,54</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 20,98</t>
+          <t>-3,61; 21,59</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-62,48; -45,31</t>
+          <t>-55,57; -41,49</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-10,86</t>
+          <t>-8,13</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-5,01</t>
+          <t>-4,33</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-6,86</t>
+          <t>-5,41</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>6,09; 21,05</t>
+          <t>6,87; 21,55</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 11,01</t>
+          <t>-2,41; 10,57</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-17,0; -4,01</t>
+          <t>-14,63; -0,9</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10,54; 18,17</t>
+          <t>10,51; 18,3</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 5,61</t>
+          <t>-1,84; 5,81</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,96; -1,57</t>
+          <t>-7,6; -0,51</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,9; 17,82</t>
+          <t>11,05; 17,64</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 5,16</t>
+          <t>-1,21; 5,52</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-9,97; -3,67</t>
+          <t>-8,53; -2,08</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-61,59%</t>
+          <t>-46,15%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-18,52%</t>
+          <t>-16,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-27,18%</t>
+          <t>-21,47%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>29,28; 144,38</t>
+          <t>30,12; 148,8</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-12,91; 77,93</t>
+          <t>-11,24; 80,19</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-81,09; -19,61</t>
+          <t>-72,8; -1,85</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>36,36; 71,74</t>
+          <t>36,43; 73,11</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 22,13</t>
+          <t>-6,5; 22,38</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-31,24; -6,39</t>
+          <t>-26,82; -1,85</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>40,62; 76,16</t>
+          <t>41,41; 73,68</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 21,44</t>
+          <t>-4,64; 23,62</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-37,22; -14,93</t>
+          <t>-32,17; -8,72</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-17,46</t>
+          <t>-15,76</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-12,62</t>
+          <t>-16,37</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-14,93</t>
+          <t>-16,04</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>13,14; 18,04</t>
+          <t>13,08; 17,86</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 4,4</t>
+          <t>-0,14; 4,24</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-20,51; -15,42</t>
+          <t>-17,74; -13,73</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14,85; 19,54</t>
+          <t>14,55; 19,38</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,78; 6,48</t>
+          <t>2,03; 6,67</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-18,0; 2,1</t>
+          <t>-18,43; -14,38</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,56; 18,1</t>
+          <t>14,57; 18,08</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,93</t>
+          <t>1,37; 4,86</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-18,0; -6,41</t>
+          <t>-17,48; -14,62</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-59,77%</t>
+          <t>-53,95%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-36,55%</t>
+          <t>-47,42%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-46,81%</t>
+          <t>-50,28%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>43,12; 64,83</t>
+          <t>43,09; 63,5</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 15,31</t>
+          <t>-0,39; 15,28</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-68,56; -54,3</t>
+          <t>-58,75; -48,8</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>41,3; 58,62</t>
+          <t>40,54; 57,95</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>4,85; 19,37</t>
+          <t>5,69; 20,0</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-51,73; 6,15</t>
+          <t>-51,5; -42,99</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>44,66; 58,37</t>
+          <t>44,26; 58,29</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>5,11; 15,92</t>
+          <t>4,15; 15,6</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-56,16; -20,36</t>
+          <t>-53,59; -46,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R2-Clase-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son no remunerados</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
